--- a/reports/tft_prediction_results.xlsx
+++ b/reports/tft_prediction_results.xlsx
@@ -511,19 +511,19 @@
         <v>23.4</v>
       </c>
       <c r="G2" t="n">
-        <v>64.65365600585938</v>
+        <v>59.74925231933594</v>
       </c>
       <c r="H2" t="n">
-        <v>64.80541229248047</v>
+        <v>55.073486328125</v>
       </c>
       <c r="I2" t="n">
-        <v>2530.16552734375</v>
+        <v>2467.5283203125</v>
       </c>
       <c r="J2" t="n">
-        <v>59.79232406616211</v>
+        <v>53.70585632324219</v>
       </c>
       <c r="K2" t="n">
-        <v>16.90903854370117</v>
+        <v>18.07442855834961</v>
       </c>
     </row>
     <row r="3">
@@ -546,19 +546,19 @@
         <v>23.5</v>
       </c>
       <c r="G3" t="n">
-        <v>56.2020263671875</v>
+        <v>52.70097351074219</v>
       </c>
       <c r="H3" t="n">
-        <v>61.30005264282227</v>
+        <v>51.13645172119141</v>
       </c>
       <c r="I3" t="n">
-        <v>2099.528076171875</v>
+        <v>1333.216430664062</v>
       </c>
       <c r="J3" t="n">
-        <v>64.9388427734375</v>
+        <v>55.67532730102539</v>
       </c>
       <c r="K3" t="n">
-        <v>14.11795520782471</v>
+        <v>13.2206335067749</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>22.9</v>
       </c>
       <c r="G4" t="n">
-        <v>61.89712524414062</v>
+        <v>67.44716644287109</v>
       </c>
       <c r="H4" t="n">
-        <v>64.27066040039062</v>
+        <v>64.02257537841797</v>
       </c>
       <c r="I4" t="n">
-        <v>2642.767333984375</v>
+        <v>1779.318237304688</v>
       </c>
       <c r="J4" t="n">
-        <v>51.39938354492188</v>
+        <v>49.13541030883789</v>
       </c>
       <c r="K4" t="n">
-        <v>18.99428749084473</v>
+        <v>18.03343772888184</v>
       </c>
     </row>
     <row r="5">
@@ -616,19 +616,19 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>62.54704284667969</v>
+        <v>74.05523681640625</v>
       </c>
       <c r="H5" t="n">
-        <v>61.77443313598633</v>
+        <v>71.88275909423828</v>
       </c>
       <c r="I5" t="n">
-        <v>1878.63916015625</v>
+        <v>1189.161987304688</v>
       </c>
       <c r="J5" t="n">
-        <v>55.03580474853516</v>
+        <v>48.65460205078125</v>
       </c>
       <c r="K5" t="n">
-        <v>19.06656265258789</v>
+        <v>16.65051078796387</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>61.09850311279297</v>
+        <v>74.58026123046875</v>
       </c>
       <c r="H6" t="n">
-        <v>62.31778717041016</v>
+        <v>76.25457000732422</v>
       </c>
       <c r="I6" t="n">
-        <v>1478.9853515625</v>
+        <v>934.002197265625</v>
       </c>
       <c r="J6" t="n">
-        <v>46.34407043457031</v>
+        <v>42.94955062866211</v>
       </c>
       <c r="K6" t="n">
-        <v>13.53823661804199</v>
+        <v>11.42043399810791</v>
       </c>
     </row>
     <row r="7">
@@ -686,19 +686,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>49.93083190917969</v>
+        <v>61.35310745239258</v>
       </c>
       <c r="H7" t="n">
-        <v>87.70808410644531</v>
+        <v>110.2657165527344</v>
       </c>
       <c r="I7" t="n">
-        <v>1105.797241210938</v>
+        <v>751.6087646484375</v>
       </c>
       <c r="J7" t="n">
-        <v>48.74736785888672</v>
+        <v>45.63566207885742</v>
       </c>
       <c r="K7" t="n">
-        <v>22.34971618652344</v>
+        <v>19.59607887268066</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>59.8266487121582</v>
+        <v>72.98283386230469</v>
       </c>
       <c r="H8" t="n">
-        <v>68.16487884521484</v>
+        <v>82.51547241210938</v>
       </c>
       <c r="I8" t="n">
-        <v>1348.689086914062</v>
+        <v>991.6757202148438</v>
       </c>
       <c r="J8" t="n">
-        <v>46.32328033447266</v>
+        <v>43.29195785522461</v>
       </c>
       <c r="K8" t="n">
-        <v>27.9713249206543</v>
+        <v>28.54887962341309</v>
       </c>
     </row>
     <row r="9">
@@ -756,19 +756,19 @@
         <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>57.84267044067383</v>
+        <v>70.95880889892578</v>
       </c>
       <c r="H9" t="n">
-        <v>80.1510009765625</v>
+        <v>98.31162261962891</v>
       </c>
       <c r="I9" t="n">
-        <v>1128.9228515625</v>
+        <v>904.0664672851562</v>
       </c>
       <c r="J9" t="n">
-        <v>28.2955379486084</v>
+        <v>24.75147819519043</v>
       </c>
       <c r="K9" t="n">
-        <v>17.36457252502441</v>
+        <v>17.07504653930664</v>
       </c>
     </row>
     <row r="10">
@@ -791,19 +791,19 @@
         <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>45.90960311889648</v>
+        <v>56.80191421508789</v>
       </c>
       <c r="H10" t="n">
-        <v>58.45135879516602</v>
+        <v>70.90772247314453</v>
       </c>
       <c r="I10" t="n">
-        <v>1035.330688476562</v>
+        <v>1011.109375</v>
       </c>
       <c r="J10" t="n">
-        <v>35.29219436645508</v>
+        <v>34.41070556640625</v>
       </c>
       <c r="K10" t="n">
-        <v>16.41268730163574</v>
+        <v>18.12965965270996</v>
       </c>
     </row>
     <row r="11">
@@ -826,19 +826,19 @@
         <v>19.8</v>
       </c>
       <c r="G11" t="n">
-        <v>57.11300277709961</v>
+        <v>68.27223205566406</v>
       </c>
       <c r="H11" t="n">
-        <v>76.24634552001953</v>
+        <v>88.88423919677734</v>
       </c>
       <c r="I11" t="n">
-        <v>1160.932373046875</v>
+        <v>1188.715698242188</v>
       </c>
       <c r="J11" t="n">
-        <v>33.13983535766602</v>
+        <v>34.08225631713867</v>
       </c>
       <c r="K11" t="n">
-        <v>21.48879623413086</v>
+        <v>23.74041366577148</v>
       </c>
     </row>
     <row r="12">
@@ -861,19 +861,19 @@
         <v>24.2</v>
       </c>
       <c r="G12" t="n">
-        <v>64.64549255371094</v>
+        <v>76.31001281738281</v>
       </c>
       <c r="H12" t="n">
-        <v>51.30139923095703</v>
+        <v>51.40607452392578</v>
       </c>
       <c r="I12" t="n">
-        <v>1292.855346679688</v>
+        <v>1452.523071289062</v>
       </c>
       <c r="J12" t="n">
-        <v>46.31076812744141</v>
+        <v>55.63755798339844</v>
       </c>
       <c r="K12" t="n">
-        <v>21.73600196838379</v>
+        <v>29.07956886291504</v>
       </c>
     </row>
     <row r="13">
@@ -896,19 +896,19 @@
         <v>30.8</v>
       </c>
       <c r="G13" t="n">
-        <v>40.79114151000977</v>
+        <v>47.10625839233398</v>
       </c>
       <c r="H13" t="n">
-        <v>46.78893280029297</v>
+        <v>50.49948883056641</v>
       </c>
       <c r="I13" t="n">
-        <v>1361.312255859375</v>
+        <v>1614.970458984375</v>
       </c>
       <c r="J13" t="n">
-        <v>30.11051940917969</v>
+        <v>37.42718887329102</v>
       </c>
       <c r="K13" t="n">
-        <v>14.99010372161865</v>
+        <v>21.7042236328125</v>
       </c>
     </row>
   </sheetData>

--- a/reports/tft_prediction_results.xlsx
+++ b/reports/tft_prediction_results.xlsx
@@ -511,19 +511,19 @@
         <v>23.4</v>
       </c>
       <c r="G2" t="n">
-        <v>59.74925231933594</v>
+        <v>64.42655944824219</v>
       </c>
       <c r="H2" t="n">
-        <v>55.073486328125</v>
+        <v>64.43955993652344</v>
       </c>
       <c r="I2" t="n">
-        <v>2467.5283203125</v>
+        <v>1938.241821289062</v>
       </c>
       <c r="J2" t="n">
-        <v>53.70585632324219</v>
+        <v>55.61983108520508</v>
       </c>
       <c r="K2" t="n">
-        <v>18.07442855834961</v>
+        <v>14.46464824676514</v>
       </c>
     </row>
     <row r="3">
@@ -546,19 +546,19 @@
         <v>23.5</v>
       </c>
       <c r="G3" t="n">
-        <v>52.70097351074219</v>
+        <v>53.9040641784668</v>
       </c>
       <c r="H3" t="n">
-        <v>51.13645172119141</v>
+        <v>59.32230377197266</v>
       </c>
       <c r="I3" t="n">
-        <v>1333.216430664062</v>
+        <v>1242.523071289062</v>
       </c>
       <c r="J3" t="n">
-        <v>55.67532730102539</v>
+        <v>58.12263107299805</v>
       </c>
       <c r="K3" t="n">
-        <v>13.2206335067749</v>
+        <v>12.24114608764648</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>22.9</v>
       </c>
       <c r="G4" t="n">
-        <v>67.44716644287109</v>
+        <v>64.69992065429688</v>
       </c>
       <c r="H4" t="n">
-        <v>64.02257537841797</v>
+        <v>67.83617401123047</v>
       </c>
       <c r="I4" t="n">
-        <v>1779.318237304688</v>
+        <v>1642.660278320312</v>
       </c>
       <c r="J4" t="n">
-        <v>49.13541030883789</v>
+        <v>48.18608474731445</v>
       </c>
       <c r="K4" t="n">
-        <v>18.03343772888184</v>
+        <v>15.74106693267822</v>
       </c>
     </row>
     <row r="5">
@@ -616,19 +616,19 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>74.05523681640625</v>
+        <v>70.093994140625</v>
       </c>
       <c r="H5" t="n">
-        <v>71.88275909423828</v>
+        <v>68.82396697998047</v>
       </c>
       <c r="I5" t="n">
-        <v>1189.161987304688</v>
+        <v>951.5116577148438</v>
       </c>
       <c r="J5" t="n">
-        <v>48.65460205078125</v>
+        <v>56.9271354675293</v>
       </c>
       <c r="K5" t="n">
-        <v>16.65051078796387</v>
+        <v>16.63080978393555</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>74.58026123046875</v>
+        <v>68.94363403320312</v>
       </c>
       <c r="H6" t="n">
-        <v>76.25457000732422</v>
+        <v>72.06621551513672</v>
       </c>
       <c r="I6" t="n">
-        <v>934.002197265625</v>
+        <v>756.8406372070312</v>
       </c>
       <c r="J6" t="n">
-        <v>42.94955062866211</v>
+        <v>52.52347564697266</v>
       </c>
       <c r="K6" t="n">
-        <v>11.42043399810791</v>
+        <v>14.83625602722168</v>
       </c>
     </row>
     <row r="7">
@@ -686,19 +686,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>61.35310745239258</v>
+        <v>58.58266830444336</v>
       </c>
       <c r="H7" t="n">
-        <v>110.2657165527344</v>
+        <v>103.9349060058594</v>
       </c>
       <c r="I7" t="n">
-        <v>751.6087646484375</v>
+        <v>591.43212890625</v>
       </c>
       <c r="J7" t="n">
-        <v>45.63566207885742</v>
+        <v>54.8891487121582</v>
       </c>
       <c r="K7" t="n">
-        <v>19.59607887268066</v>
+        <v>21.59616661071777</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>72.98283386230469</v>
+        <v>71.37654876708984</v>
       </c>
       <c r="H8" t="n">
-        <v>82.51547241210938</v>
+        <v>87.59488677978516</v>
       </c>
       <c r="I8" t="n">
-        <v>991.6757202148438</v>
+        <v>736.7465209960938</v>
       </c>
       <c r="J8" t="n">
-        <v>43.29195785522461</v>
+        <v>52.74888610839844</v>
       </c>
       <c r="K8" t="n">
-        <v>28.54887962341309</v>
+        <v>28.37335968017578</v>
       </c>
     </row>
     <row r="9">
@@ -756,19 +756,19 @@
         <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>70.95880889892578</v>
+        <v>70.58931732177734</v>
       </c>
       <c r="H9" t="n">
-        <v>98.31162261962891</v>
+        <v>99.96483612060547</v>
       </c>
       <c r="I9" t="n">
-        <v>904.0664672851562</v>
+        <v>640.0484008789062</v>
       </c>
       <c r="J9" t="n">
-        <v>24.75147819519043</v>
+        <v>33.28680038452148</v>
       </c>
       <c r="K9" t="n">
-        <v>17.07504653930664</v>
+        <v>18.66464996337891</v>
       </c>
     </row>
     <row r="10">
@@ -791,19 +791,19 @@
         <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>56.80191421508789</v>
+        <v>56.36387252807617</v>
       </c>
       <c r="H10" t="n">
-        <v>70.90772247314453</v>
+        <v>70.02207946777344</v>
       </c>
       <c r="I10" t="n">
-        <v>1011.109375</v>
+        <v>872.8863525390625</v>
       </c>
       <c r="J10" t="n">
-        <v>34.41070556640625</v>
+        <v>39.64035797119141</v>
       </c>
       <c r="K10" t="n">
-        <v>18.12965965270996</v>
+        <v>20.01910591125488</v>
       </c>
     </row>
     <row r="11">
@@ -826,19 +826,19 @@
         <v>19.8</v>
       </c>
       <c r="G11" t="n">
-        <v>68.27223205566406</v>
+        <v>68.07434844970703</v>
       </c>
       <c r="H11" t="n">
-        <v>88.88423919677734</v>
+        <v>91.49615478515625</v>
       </c>
       <c r="I11" t="n">
-        <v>1188.715698242188</v>
+        <v>1008.091491699219</v>
       </c>
       <c r="J11" t="n">
-        <v>34.08225631713867</v>
+        <v>38.17132949829102</v>
       </c>
       <c r="K11" t="n">
-        <v>23.74041366577148</v>
+        <v>25.81139755249023</v>
       </c>
     </row>
     <row r="12">
@@ -861,19 +861,19 @@
         <v>24.2</v>
       </c>
       <c r="G12" t="n">
-        <v>76.31001281738281</v>
+        <v>75.62937927246094</v>
       </c>
       <c r="H12" t="n">
-        <v>51.40607452392578</v>
+        <v>54.29406356811523</v>
       </c>
       <c r="I12" t="n">
-        <v>1452.523071289062</v>
+        <v>1134.9912109375</v>
       </c>
       <c r="J12" t="n">
-        <v>55.63755798339844</v>
+        <v>50.70816421508789</v>
       </c>
       <c r="K12" t="n">
-        <v>29.07956886291504</v>
+        <v>25.74802017211914</v>
       </c>
     </row>
     <row r="13">
@@ -896,19 +896,19 @@
         <v>30.8</v>
       </c>
       <c r="G13" t="n">
-        <v>47.10625839233398</v>
+        <v>42.46371459960938</v>
       </c>
       <c r="H13" t="n">
-        <v>50.49948883056641</v>
+        <v>45.44647979736328</v>
       </c>
       <c r="I13" t="n">
-        <v>1614.970458984375</v>
+        <v>1108.903198242188</v>
       </c>
       <c r="J13" t="n">
-        <v>37.42718887329102</v>
+        <v>37.79124450683594</v>
       </c>
       <c r="K13" t="n">
-        <v>21.7042236328125</v>
+        <v>18.31354141235352</v>
       </c>
     </row>
   </sheetData>

--- a/reports/tft_prediction_results.xlsx
+++ b/reports/tft_prediction_results.xlsx
@@ -511,19 +511,19 @@
         <v>23.4</v>
       </c>
       <c r="G2" t="n">
-        <v>64.42655944824219</v>
+        <v>60.19683074951172</v>
       </c>
       <c r="H2" t="n">
-        <v>64.43955993652344</v>
+        <v>59.11296081542969</v>
       </c>
       <c r="I2" t="n">
-        <v>1938.241821289062</v>
+        <v>2726.3583984375</v>
       </c>
       <c r="J2" t="n">
-        <v>55.61983108520508</v>
+        <v>64.98369598388672</v>
       </c>
       <c r="K2" t="n">
-        <v>14.46464824676514</v>
+        <v>22.10103416442871</v>
       </c>
     </row>
     <row r="3">
@@ -546,19 +546,19 @@
         <v>23.5</v>
       </c>
       <c r="G3" t="n">
-        <v>53.9040641784668</v>
+        <v>49.44652557373047</v>
       </c>
       <c r="H3" t="n">
-        <v>59.32230377197266</v>
+        <v>51.20060348510742</v>
       </c>
       <c r="I3" t="n">
-        <v>1242.523071289062</v>
+        <v>2319.488525390625</v>
       </c>
       <c r="J3" t="n">
-        <v>58.12263107299805</v>
+        <v>67.93243408203125</v>
       </c>
       <c r="K3" t="n">
-        <v>12.24114608764648</v>
+        <v>18.38014793395996</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>22.9</v>
       </c>
       <c r="G4" t="n">
-        <v>64.69992065429688</v>
+        <v>58.5441780090332</v>
       </c>
       <c r="H4" t="n">
-        <v>67.83617401123047</v>
+        <v>60.54452133178711</v>
       </c>
       <c r="I4" t="n">
-        <v>1642.660278320312</v>
+        <v>2805.3623046875</v>
       </c>
       <c r="J4" t="n">
-        <v>48.18608474731445</v>
+        <v>56.9476318359375</v>
       </c>
       <c r="K4" t="n">
-        <v>15.74106693267822</v>
+        <v>20.71495628356934</v>
       </c>
     </row>
     <row r="5">
@@ -616,19 +616,19 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>70.093994140625</v>
+        <v>63.28344345092773</v>
       </c>
       <c r="H5" t="n">
-        <v>68.82396697998047</v>
+        <v>59.86714935302734</v>
       </c>
       <c r="I5" t="n">
-        <v>951.5116577148438</v>
+        <v>2274.095947265625</v>
       </c>
       <c r="J5" t="n">
-        <v>56.9271354675293</v>
+        <v>64.84127044677734</v>
       </c>
       <c r="K5" t="n">
-        <v>16.63080978393555</v>
+        <v>18.87285614013672</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>68.94363403320312</v>
+        <v>61.78500366210938</v>
       </c>
       <c r="H6" t="n">
-        <v>72.06621551513672</v>
+        <v>60.83145141601562</v>
       </c>
       <c r="I6" t="n">
-        <v>756.8406372070312</v>
+        <v>1843.542236328125</v>
       </c>
       <c r="J6" t="n">
-        <v>52.52347564697266</v>
+        <v>58.63798141479492</v>
       </c>
       <c r="K6" t="n">
-        <v>14.83625602722168</v>
+        <v>14.25313949584961</v>
       </c>
     </row>
     <row r="7">
@@ -686,19 +686,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>58.58266830444336</v>
+        <v>51.44674301147461</v>
       </c>
       <c r="H7" t="n">
-        <v>103.9349060058594</v>
+        <v>87.60549163818359</v>
       </c>
       <c r="I7" t="n">
-        <v>591.43212890625</v>
+        <v>1404.7568359375</v>
       </c>
       <c r="J7" t="n">
-        <v>54.8891487121582</v>
+        <v>58.31808471679688</v>
       </c>
       <c r="K7" t="n">
-        <v>21.59616661071777</v>
+        <v>19.77682113647461</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>71.37654876708984</v>
+        <v>63.25297927856445</v>
       </c>
       <c r="H8" t="n">
-        <v>87.59488677978516</v>
+        <v>69.21698760986328</v>
       </c>
       <c r="I8" t="n">
-        <v>736.7465209960938</v>
+        <v>1480.195678710938</v>
       </c>
       <c r="J8" t="n">
-        <v>52.74888610839844</v>
+        <v>53.81652069091797</v>
       </c>
       <c r="K8" t="n">
-        <v>28.37335968017578</v>
+        <v>22.80734634399414</v>
       </c>
     </row>
     <row r="9">
@@ -756,19 +756,19 @@
         <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>70.58931732177734</v>
+        <v>62.37001037597656</v>
       </c>
       <c r="H9" t="n">
-        <v>99.96483612060547</v>
+        <v>81.07339477539062</v>
       </c>
       <c r="I9" t="n">
-        <v>640.0484008789062</v>
+        <v>1198.7666015625</v>
       </c>
       <c r="J9" t="n">
-        <v>33.28680038452148</v>
+        <v>30.68264770507812</v>
       </c>
       <c r="K9" t="n">
-        <v>18.66464996337891</v>
+        <v>15.09191226959229</v>
       </c>
     </row>
     <row r="10">
@@ -791,19 +791,19 @@
         <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>56.36387252807617</v>
+        <v>45.62545776367188</v>
       </c>
       <c r="H10" t="n">
-        <v>70.02207946777344</v>
+        <v>55.25712585449219</v>
       </c>
       <c r="I10" t="n">
-        <v>872.8863525390625</v>
+        <v>1207.498779296875</v>
       </c>
       <c r="J10" t="n">
-        <v>39.64035797119141</v>
+        <v>41.40956497192383</v>
       </c>
       <c r="K10" t="n">
-        <v>20.01910591125488</v>
+        <v>16.39811897277832</v>
       </c>
     </row>
     <row r="11">
@@ -826,19 +826,19 @@
         <v>19.8</v>
       </c>
       <c r="G11" t="n">
-        <v>68.07434844970703</v>
+        <v>58.44701766967773</v>
       </c>
       <c r="H11" t="n">
-        <v>91.49615478515625</v>
+        <v>74.82875061035156</v>
       </c>
       <c r="I11" t="n">
-        <v>1008.091491699219</v>
+        <v>1257.2353515625</v>
       </c>
       <c r="J11" t="n">
-        <v>38.17132949829102</v>
+        <v>39.24657821655273</v>
       </c>
       <c r="K11" t="n">
-        <v>25.81139755249023</v>
+        <v>24.67141914367676</v>
       </c>
     </row>
     <row r="12">
@@ -861,19 +861,19 @@
         <v>24.2</v>
       </c>
       <c r="G12" t="n">
-        <v>75.62937927246094</v>
+        <v>72.98086547851562</v>
       </c>
       <c r="H12" t="n">
-        <v>54.29406356811523</v>
+        <v>52.02031326293945</v>
       </c>
       <c r="I12" t="n">
-        <v>1134.9912109375</v>
+        <v>1541.739501953125</v>
       </c>
       <c r="J12" t="n">
-        <v>50.70816421508789</v>
+        <v>56.93103408813477</v>
       </c>
       <c r="K12" t="n">
-        <v>25.74802017211914</v>
+        <v>28.61232376098633</v>
       </c>
     </row>
     <row r="13">
@@ -896,19 +896,19 @@
         <v>30.8</v>
       </c>
       <c r="G13" t="n">
-        <v>42.46371459960938</v>
+        <v>52.46704864501953</v>
       </c>
       <c r="H13" t="n">
-        <v>45.44647979736328</v>
+        <v>51.86177825927734</v>
       </c>
       <c r="I13" t="n">
-        <v>1108.903198242188</v>
+        <v>1698.80908203125</v>
       </c>
       <c r="J13" t="n">
-        <v>37.79124450683594</v>
+        <v>39.38096618652344</v>
       </c>
       <c r="K13" t="n">
-        <v>18.31354141235352</v>
+        <v>19.67497253417969</v>
       </c>
     </row>
   </sheetData>

--- a/reports/tft_prediction_results.xlsx
+++ b/reports/tft_prediction_results.xlsx
@@ -511,19 +511,19 @@
         <v>23.4</v>
       </c>
       <c r="G2" t="n">
-        <v>60.19683074951172</v>
+        <v>61.8960075378418</v>
       </c>
       <c r="H2" t="n">
-        <v>59.11296081542969</v>
+        <v>65.54308319091797</v>
       </c>
       <c r="I2" t="n">
-        <v>2726.3583984375</v>
+        <v>3003.5888671875</v>
       </c>
       <c r="J2" t="n">
-        <v>64.98369598388672</v>
+        <v>61.81085205078125</v>
       </c>
       <c r="K2" t="n">
-        <v>22.10103416442871</v>
+        <v>23.25504875183105</v>
       </c>
     </row>
     <row r="3">
@@ -546,19 +546,19 @@
         <v>23.5</v>
       </c>
       <c r="G3" t="n">
-        <v>49.44652557373047</v>
+        <v>50.13015747070312</v>
       </c>
       <c r="H3" t="n">
-        <v>51.20060348510742</v>
+        <v>56.07196807861328</v>
       </c>
       <c r="I3" t="n">
-        <v>2319.488525390625</v>
+        <v>2380.69970703125</v>
       </c>
       <c r="J3" t="n">
-        <v>67.93243408203125</v>
+        <v>65.35623931884766</v>
       </c>
       <c r="K3" t="n">
-        <v>18.38014793395996</v>
+        <v>18.88390350341797</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>22.9</v>
       </c>
       <c r="G4" t="n">
-        <v>58.5441780090332</v>
+        <v>58.68259429931641</v>
       </c>
       <c r="H4" t="n">
-        <v>60.54452133178711</v>
+        <v>60.6070671081543</v>
       </c>
       <c r="I4" t="n">
-        <v>2805.3623046875</v>
+        <v>2943.190185546875</v>
       </c>
       <c r="J4" t="n">
-        <v>56.9476318359375</v>
+        <v>53.73260498046875</v>
       </c>
       <c r="K4" t="n">
-        <v>20.71495628356934</v>
+        <v>21.5560188293457</v>
       </c>
     </row>
     <row r="5">
@@ -616,19 +616,19 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>63.28344345092773</v>
+        <v>64.94483947753906</v>
       </c>
       <c r="H5" t="n">
-        <v>59.86714935302734</v>
+        <v>56.60215759277344</v>
       </c>
       <c r="I5" t="n">
-        <v>2274.095947265625</v>
+        <v>1824.028564453125</v>
       </c>
       <c r="J5" t="n">
-        <v>64.84127044677734</v>
+        <v>67.10982513427734</v>
       </c>
       <c r="K5" t="n">
-        <v>18.87285614013672</v>
+        <v>20.6135311126709</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>61.78500366210938</v>
+        <v>60.48190307617188</v>
       </c>
       <c r="H6" t="n">
-        <v>60.83145141601562</v>
+        <v>57.14858627319336</v>
       </c>
       <c r="I6" t="n">
-        <v>1843.542236328125</v>
+        <v>1328.324951171875</v>
       </c>
       <c r="J6" t="n">
-        <v>58.63798141479492</v>
+        <v>60.26732635498047</v>
       </c>
       <c r="K6" t="n">
-        <v>14.25313949584961</v>
+        <v>14.34417533874512</v>
       </c>
     </row>
     <row r="7">
@@ -686,19 +686,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>51.44674301147461</v>
+        <v>45.9317741394043</v>
       </c>
       <c r="H7" t="n">
-        <v>87.60549163818359</v>
+        <v>85.01435089111328</v>
       </c>
       <c r="I7" t="n">
-        <v>1404.7568359375</v>
+        <v>974.21044921875</v>
       </c>
       <c r="J7" t="n">
-        <v>58.31808471679688</v>
+        <v>61.61138916015625</v>
       </c>
       <c r="K7" t="n">
-        <v>19.77682113647461</v>
+        <v>21.20663070678711</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>63.25297927856445</v>
+        <v>55.15027236938477</v>
       </c>
       <c r="H8" t="n">
-        <v>69.21698760986328</v>
+        <v>60.95623779296875</v>
       </c>
       <c r="I8" t="n">
-        <v>1480.195678710938</v>
+        <v>1186.567138671875</v>
       </c>
       <c r="J8" t="n">
-        <v>53.81652069091797</v>
+        <v>56.31321334838867</v>
       </c>
       <c r="K8" t="n">
-        <v>22.80734634399414</v>
+        <v>26.22917175292969</v>
       </c>
     </row>
     <row r="9">
@@ -756,19 +756,19 @@
         <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>62.37001037597656</v>
+        <v>52.84761810302734</v>
       </c>
       <c r="H9" t="n">
-        <v>81.07339477539062</v>
+        <v>73.16828155517578</v>
       </c>
       <c r="I9" t="n">
-        <v>1198.7666015625</v>
+        <v>1045.286499023438</v>
       </c>
       <c r="J9" t="n">
-        <v>30.68264770507812</v>
+        <v>28.51273727416992</v>
       </c>
       <c r="K9" t="n">
-        <v>15.09191226959229</v>
+        <v>15.52201747894287</v>
       </c>
     </row>
     <row r="10">
@@ -791,19 +791,19 @@
         <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>45.62545776367188</v>
+        <v>38.22671127319336</v>
       </c>
       <c r="H10" t="n">
-        <v>55.25712585449219</v>
+        <v>49.96469879150391</v>
       </c>
       <c r="I10" t="n">
-        <v>1207.498779296875</v>
+        <v>1131.409057617188</v>
       </c>
       <c r="J10" t="n">
-        <v>41.40956497192383</v>
+        <v>41.42183303833008</v>
       </c>
       <c r="K10" t="n">
-        <v>16.39811897277832</v>
+        <v>16.57334899902344</v>
       </c>
     </row>
     <row r="11">
@@ -826,19 +826,19 @@
         <v>19.8</v>
       </c>
       <c r="G11" t="n">
-        <v>58.44701766967773</v>
+        <v>51.37279891967773</v>
       </c>
       <c r="H11" t="n">
-        <v>74.82875061035156</v>
+        <v>70.69995880126953</v>
       </c>
       <c r="I11" t="n">
-        <v>1257.2353515625</v>
+        <v>1357.457641601562</v>
       </c>
       <c r="J11" t="n">
-        <v>39.24657821655273</v>
+        <v>40.41432571411133</v>
       </c>
       <c r="K11" t="n">
-        <v>24.67141914367676</v>
+        <v>23.39736366271973</v>
       </c>
     </row>
     <row r="12">
@@ -861,19 +861,19 @@
         <v>24.2</v>
       </c>
       <c r="G12" t="n">
-        <v>72.98086547851562</v>
+        <v>76.15496826171875</v>
       </c>
       <c r="H12" t="n">
-        <v>52.02031326293945</v>
+        <v>55.49580383300781</v>
       </c>
       <c r="I12" t="n">
-        <v>1541.739501953125</v>
+        <v>1659.495361328125</v>
       </c>
       <c r="J12" t="n">
-        <v>56.93103408813477</v>
+        <v>60.04635238647461</v>
       </c>
       <c r="K12" t="n">
-        <v>28.61232376098633</v>
+        <v>26.71347236633301</v>
       </c>
     </row>
     <row r="13">
@@ -896,19 +896,19 @@
         <v>30.8</v>
       </c>
       <c r="G13" t="n">
-        <v>52.46704864501953</v>
+        <v>47.610107421875</v>
       </c>
       <c r="H13" t="n">
-        <v>51.86177825927734</v>
+        <v>49.51117324829102</v>
       </c>
       <c r="I13" t="n">
-        <v>1698.80908203125</v>
+        <v>1471.333984375</v>
       </c>
       <c r="J13" t="n">
-        <v>39.38096618652344</v>
+        <v>44.11598205566406</v>
       </c>
       <c r="K13" t="n">
-        <v>19.67497253417969</v>
+        <v>21.49010276794434</v>
       </c>
     </row>
   </sheetData>

--- a/reports/tft_prediction_results.xlsx
+++ b/reports/tft_prediction_results.xlsx
@@ -511,19 +511,19 @@
         <v>23.4</v>
       </c>
       <c r="G2" t="n">
-        <v>61.8960075378418</v>
+        <v>53.30074310302734</v>
       </c>
       <c r="H2" t="n">
-        <v>65.54308319091797</v>
+        <v>55.21882629394531</v>
       </c>
       <c r="I2" t="n">
-        <v>3003.5888671875</v>
+        <v>2413.17724609375</v>
       </c>
       <c r="J2" t="n">
-        <v>61.81085205078125</v>
+        <v>59.48630905151367</v>
       </c>
       <c r="K2" t="n">
-        <v>23.25504875183105</v>
+        <v>17.24643325805664</v>
       </c>
     </row>
     <row r="3">
@@ -546,19 +546,19 @@
         <v>23.5</v>
       </c>
       <c r="G3" t="n">
-        <v>50.13015747070312</v>
+        <v>45.15597534179688</v>
       </c>
       <c r="H3" t="n">
-        <v>56.07196807861328</v>
+        <v>50.84686660766602</v>
       </c>
       <c r="I3" t="n">
-        <v>2380.69970703125</v>
+        <v>1826.947509765625</v>
       </c>
       <c r="J3" t="n">
-        <v>65.35623931884766</v>
+        <v>61.18750381469727</v>
       </c>
       <c r="K3" t="n">
-        <v>18.88390350341797</v>
+        <v>12.52735710144043</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>22.9</v>
       </c>
       <c r="G4" t="n">
-        <v>58.68259429931641</v>
+        <v>53.88619613647461</v>
       </c>
       <c r="H4" t="n">
-        <v>60.6070671081543</v>
+        <v>57.6845588684082</v>
       </c>
       <c r="I4" t="n">
-        <v>2943.190185546875</v>
+        <v>2347.484619140625</v>
       </c>
       <c r="J4" t="n">
-        <v>53.73260498046875</v>
+        <v>55.1367301940918</v>
       </c>
       <c r="K4" t="n">
-        <v>21.5560188293457</v>
+        <v>15.21408843994141</v>
       </c>
     </row>
     <row r="5">
@@ -616,19 +616,19 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>64.94483947753906</v>
+        <v>54.90773010253906</v>
       </c>
       <c r="H5" t="n">
-        <v>56.60215759277344</v>
+        <v>55.02166748046875</v>
       </c>
       <c r="I5" t="n">
-        <v>1824.028564453125</v>
+        <v>1802.957275390625</v>
       </c>
       <c r="J5" t="n">
-        <v>67.10982513427734</v>
+        <v>50.2429313659668</v>
       </c>
       <c r="K5" t="n">
-        <v>20.6135311126709</v>
+        <v>15.32516765594482</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>60.48190307617188</v>
+        <v>57.64475250244141</v>
       </c>
       <c r="H6" t="n">
-        <v>57.14858627319336</v>
+        <v>57.5975227355957</v>
       </c>
       <c r="I6" t="n">
-        <v>1328.324951171875</v>
+        <v>1296.728393554688</v>
       </c>
       <c r="J6" t="n">
-        <v>60.26732635498047</v>
+        <v>46.37667083740234</v>
       </c>
       <c r="K6" t="n">
-        <v>14.34417533874512</v>
+        <v>11.85456657409668</v>
       </c>
     </row>
     <row r="7">
@@ -686,19 +686,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>45.9317741394043</v>
+        <v>48.05370712280273</v>
       </c>
       <c r="H7" t="n">
-        <v>85.01435089111328</v>
+        <v>84.39467620849609</v>
       </c>
       <c r="I7" t="n">
-        <v>974.21044921875</v>
+        <v>921.4318237304688</v>
       </c>
       <c r="J7" t="n">
-        <v>61.61138916015625</v>
+        <v>49.54742050170898</v>
       </c>
       <c r="K7" t="n">
-        <v>21.20663070678711</v>
+        <v>19.42214775085449</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>55.15027236938477</v>
+        <v>62.78534317016602</v>
       </c>
       <c r="H8" t="n">
-        <v>60.95623779296875</v>
+        <v>70.60076904296875</v>
       </c>
       <c r="I8" t="n">
-        <v>1186.567138671875</v>
+        <v>1234.6328125</v>
       </c>
       <c r="J8" t="n">
-        <v>56.31321334838867</v>
+        <v>50.59278106689453</v>
       </c>
       <c r="K8" t="n">
-        <v>26.22917175292969</v>
+        <v>24.61614418029785</v>
       </c>
     </row>
     <row r="9">
@@ -756,19 +756,19 @@
         <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>52.84761810302734</v>
+        <v>63.7049560546875</v>
       </c>
       <c r="H9" t="n">
-        <v>73.16828155517578</v>
+        <v>85.55424499511719</v>
       </c>
       <c r="I9" t="n">
-        <v>1045.286499023438</v>
+        <v>1103.9287109375</v>
       </c>
       <c r="J9" t="n">
-        <v>28.51273727416992</v>
+        <v>31.61293983459473</v>
       </c>
       <c r="K9" t="n">
-        <v>15.52201747894287</v>
+        <v>17.94906044006348</v>
       </c>
     </row>
     <row r="10">
@@ -791,19 +791,19 @@
         <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>38.22671127319336</v>
+        <v>52.85435104370117</v>
       </c>
       <c r="H10" t="n">
-        <v>49.96469879150391</v>
+        <v>62.9311637878418</v>
       </c>
       <c r="I10" t="n">
-        <v>1131.409057617188</v>
+        <v>1077.859985351562</v>
       </c>
       <c r="J10" t="n">
-        <v>41.42183303833008</v>
+        <v>47.87376022338867</v>
       </c>
       <c r="K10" t="n">
-        <v>16.57334899902344</v>
+        <v>21.67433738708496</v>
       </c>
     </row>
     <row r="11">
@@ -826,19 +826,19 @@
         <v>19.8</v>
       </c>
       <c r="G11" t="n">
-        <v>51.37279891967773</v>
+        <v>68.15695190429688</v>
       </c>
       <c r="H11" t="n">
-        <v>70.69995880126953</v>
+        <v>86.96096801757812</v>
       </c>
       <c r="I11" t="n">
-        <v>1357.457641601562</v>
+        <v>1137.883178710938</v>
       </c>
       <c r="J11" t="n">
-        <v>40.41432571411133</v>
+        <v>43.62075424194336</v>
       </c>
       <c r="K11" t="n">
-        <v>23.39736366271973</v>
+        <v>31.87233352661133</v>
       </c>
     </row>
     <row r="12">
@@ -861,19 +861,19 @@
         <v>24.2</v>
       </c>
       <c r="G12" t="n">
-        <v>76.15496826171875</v>
+        <v>69.30111694335938</v>
       </c>
       <c r="H12" t="n">
-        <v>55.49580383300781</v>
+        <v>50.31573104858398</v>
       </c>
       <c r="I12" t="n">
-        <v>1659.495361328125</v>
+        <v>1435.561767578125</v>
       </c>
       <c r="J12" t="n">
-        <v>60.04635238647461</v>
+        <v>56.9250373840332</v>
       </c>
       <c r="K12" t="n">
-        <v>26.71347236633301</v>
+        <v>34.03376388549805</v>
       </c>
     </row>
     <row r="13">
@@ -896,19 +896,19 @@
         <v>30.8</v>
       </c>
       <c r="G13" t="n">
-        <v>47.610107421875</v>
+        <v>37.3889274597168</v>
       </c>
       <c r="H13" t="n">
-        <v>49.51117324829102</v>
+        <v>44.77835464477539</v>
       </c>
       <c r="I13" t="n">
-        <v>1471.333984375</v>
+        <v>1608.333618164062</v>
       </c>
       <c r="J13" t="n">
-        <v>44.11598205566406</v>
+        <v>39.47692489624023</v>
       </c>
       <c r="K13" t="n">
-        <v>21.49010276794434</v>
+        <v>21.64213562011719</v>
       </c>
     </row>
   </sheetData>

--- a/reports/tft_prediction_results.xlsx
+++ b/reports/tft_prediction_results.xlsx
@@ -511,19 +511,19 @@
         <v>23.4</v>
       </c>
       <c r="G2" t="n">
-        <v>53.30074310302734</v>
+        <v>59.92309188842773</v>
       </c>
       <c r="H2" t="n">
-        <v>55.21882629394531</v>
+        <v>58.63067626953125</v>
       </c>
       <c r="I2" t="n">
-        <v>2413.17724609375</v>
+        <v>2595.279541015625</v>
       </c>
       <c r="J2" t="n">
-        <v>59.48630905151367</v>
+        <v>60.75212097167969</v>
       </c>
       <c r="K2" t="n">
-        <v>17.24643325805664</v>
+        <v>14.79060935974121</v>
       </c>
     </row>
     <row r="3">
@@ -546,19 +546,19 @@
         <v>23.5</v>
       </c>
       <c r="G3" t="n">
-        <v>45.15597534179688</v>
+        <v>48.20302963256836</v>
       </c>
       <c r="H3" t="n">
-        <v>50.84686660766602</v>
+        <v>50.5529670715332</v>
       </c>
       <c r="I3" t="n">
-        <v>1826.947509765625</v>
+        <v>1882.999877929688</v>
       </c>
       <c r="J3" t="n">
-        <v>61.18750381469727</v>
+        <v>65.69202423095703</v>
       </c>
       <c r="K3" t="n">
-        <v>12.52735710144043</v>
+        <v>9.116301536560059</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>22.9</v>
       </c>
       <c r="G4" t="n">
-        <v>53.88619613647461</v>
+        <v>55.65500259399414</v>
       </c>
       <c r="H4" t="n">
-        <v>57.6845588684082</v>
+        <v>56.5267448425293</v>
       </c>
       <c r="I4" t="n">
-        <v>2347.484619140625</v>
+        <v>2640.345458984375</v>
       </c>
       <c r="J4" t="n">
-        <v>55.1367301940918</v>
+        <v>54.58597564697266</v>
       </c>
       <c r="K4" t="n">
-        <v>15.21408843994141</v>
+        <v>10.33656978607178</v>
       </c>
     </row>
     <row r="5">
@@ -616,19 +616,19 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>54.90773010253906</v>
+        <v>59.92533493041992</v>
       </c>
       <c r="H5" t="n">
-        <v>55.02166748046875</v>
+        <v>56.98447799682617</v>
       </c>
       <c r="I5" t="n">
-        <v>1802.957275390625</v>
+        <v>2143.89453125</v>
       </c>
       <c r="J5" t="n">
-        <v>50.2429313659668</v>
+        <v>57.37261581420898</v>
       </c>
       <c r="K5" t="n">
-        <v>15.32516765594482</v>
+        <v>9.22816276550293</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>57.64475250244141</v>
+        <v>56.97018051147461</v>
       </c>
       <c r="H6" t="n">
-        <v>57.5975227355957</v>
+        <v>58.22603988647461</v>
       </c>
       <c r="I6" t="n">
-        <v>1296.728393554688</v>
+        <v>1715.078979492188</v>
       </c>
       <c r="J6" t="n">
-        <v>46.37667083740234</v>
+        <v>49.42683792114258</v>
       </c>
       <c r="K6" t="n">
-        <v>11.85456657409668</v>
+        <v>6.28036642074585</v>
       </c>
     </row>
     <row r="7">
@@ -686,19 +686,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>48.05370712280273</v>
+        <v>42.50269317626953</v>
       </c>
       <c r="H7" t="n">
-        <v>84.39467620849609</v>
+        <v>87.46645355224609</v>
       </c>
       <c r="I7" t="n">
-        <v>921.4318237304688</v>
+        <v>1342.947875976562</v>
       </c>
       <c r="J7" t="n">
-        <v>49.54742050170898</v>
+        <v>50.9345588684082</v>
       </c>
       <c r="K7" t="n">
-        <v>19.42214775085449</v>
+        <v>14.04294776916504</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>62.78534317016602</v>
+        <v>55.01007843017578</v>
       </c>
       <c r="H8" t="n">
-        <v>70.60076904296875</v>
+        <v>68.51380157470703</v>
       </c>
       <c r="I8" t="n">
-        <v>1234.6328125</v>
+        <v>1633.667358398438</v>
       </c>
       <c r="J8" t="n">
-        <v>50.59278106689453</v>
+        <v>49.10960388183594</v>
       </c>
       <c r="K8" t="n">
-        <v>24.61614418029785</v>
+        <v>18.39679718017578</v>
       </c>
     </row>
     <row r="9">
@@ -756,19 +756,19 @@
         <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>63.7049560546875</v>
+        <v>54.21974945068359</v>
       </c>
       <c r="H9" t="n">
-        <v>85.55424499511719</v>
+        <v>81.57511138916016</v>
       </c>
       <c r="I9" t="n">
-        <v>1103.9287109375</v>
+        <v>1374.293090820312</v>
       </c>
       <c r="J9" t="n">
-        <v>31.61293983459473</v>
+        <v>26.4704647064209</v>
       </c>
       <c r="K9" t="n">
-        <v>17.94906044006348</v>
+        <v>11.9194860458374</v>
       </c>
     </row>
     <row r="10">
@@ -791,19 +791,19 @@
         <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>52.85435104370117</v>
+        <v>36.63339233398438</v>
       </c>
       <c r="H10" t="n">
-        <v>62.9311637878418</v>
+        <v>57.39704895019531</v>
       </c>
       <c r="I10" t="n">
-        <v>1077.859985351562</v>
+        <v>1145.97314453125</v>
       </c>
       <c r="J10" t="n">
-        <v>47.87376022338867</v>
+        <v>48.41079330444336</v>
       </c>
       <c r="K10" t="n">
-        <v>21.67433738708496</v>
+        <v>13.73410797119141</v>
       </c>
     </row>
     <row r="11">
@@ -826,19 +826,19 @@
         <v>19.8</v>
       </c>
       <c r="G11" t="n">
-        <v>68.15695190429688</v>
+        <v>50.51754379272461</v>
       </c>
       <c r="H11" t="n">
-        <v>86.96096801757812</v>
+        <v>82.83078765869141</v>
       </c>
       <c r="I11" t="n">
-        <v>1137.883178710938</v>
+        <v>1511.091552734375</v>
       </c>
       <c r="J11" t="n">
-        <v>43.62075424194336</v>
+        <v>49.19083023071289</v>
       </c>
       <c r="K11" t="n">
-        <v>31.87233352661133</v>
+        <v>24.22340774536133</v>
       </c>
     </row>
     <row r="12">
@@ -861,19 +861,19 @@
         <v>24.2</v>
       </c>
       <c r="G12" t="n">
-        <v>69.30111694335938</v>
+        <v>54.67883682250977</v>
       </c>
       <c r="H12" t="n">
-        <v>50.31573104858398</v>
+        <v>51.59475326538086</v>
       </c>
       <c r="I12" t="n">
-        <v>1435.561767578125</v>
+        <v>1630.75732421875</v>
       </c>
       <c r="J12" t="n">
-        <v>56.9250373840332</v>
+        <v>71.45391082763672</v>
       </c>
       <c r="K12" t="n">
-        <v>34.03376388549805</v>
+        <v>29.63018226623535</v>
       </c>
     </row>
     <row r="13">
@@ -896,19 +896,19 @@
         <v>30.8</v>
       </c>
       <c r="G13" t="n">
-        <v>37.3889274597168</v>
+        <v>37.83502578735352</v>
       </c>
       <c r="H13" t="n">
-        <v>44.77835464477539</v>
+        <v>47.95979309082031</v>
       </c>
       <c r="I13" t="n">
-        <v>1608.333618164062</v>
+        <v>1404.318359375</v>
       </c>
       <c r="J13" t="n">
-        <v>39.47692489624023</v>
+        <v>46.89516830444336</v>
       </c>
       <c r="K13" t="n">
-        <v>21.64213562011719</v>
+        <v>23.43389129638672</v>
       </c>
     </row>
   </sheetData>

--- a/reports/tft_prediction_results.xlsx
+++ b/reports/tft_prediction_results.xlsx
@@ -511,19 +511,19 @@
         <v>23.4</v>
       </c>
       <c r="G2" t="n">
-        <v>59.92309188842773</v>
+        <v>68.18646240234375</v>
       </c>
       <c r="H2" t="n">
-        <v>58.63067626953125</v>
+        <v>74.13885498046875</v>
       </c>
       <c r="I2" t="n">
-        <v>2595.279541015625</v>
+        <v>2738.91748046875</v>
       </c>
       <c r="J2" t="n">
-        <v>60.75212097167969</v>
+        <v>66.79878234863281</v>
       </c>
       <c r="K2" t="n">
-        <v>14.79060935974121</v>
+        <v>19.88101196289062</v>
       </c>
     </row>
     <row r="3">
@@ -546,19 +546,19 @@
         <v>23.5</v>
       </c>
       <c r="G3" t="n">
-        <v>48.20302963256836</v>
+        <v>61.11162185668945</v>
       </c>
       <c r="H3" t="n">
-        <v>50.5529670715332</v>
+        <v>69.56171417236328</v>
       </c>
       <c r="I3" t="n">
-        <v>1882.999877929688</v>
+        <v>2138.39892578125</v>
       </c>
       <c r="J3" t="n">
-        <v>65.69202423095703</v>
+        <v>71.78091430664062</v>
       </c>
       <c r="K3" t="n">
-        <v>9.116301536560059</v>
+        <v>15.04044628143311</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>22.9</v>
       </c>
       <c r="G4" t="n">
-        <v>55.65500259399414</v>
+        <v>74.85029602050781</v>
       </c>
       <c r="H4" t="n">
-        <v>56.5267448425293</v>
+        <v>84.09366607666016</v>
       </c>
       <c r="I4" t="n">
-        <v>2640.345458984375</v>
+        <v>2926.63427734375</v>
       </c>
       <c r="J4" t="n">
-        <v>54.58597564697266</v>
+        <v>60.92645263671875</v>
       </c>
       <c r="K4" t="n">
-        <v>10.33656978607178</v>
+        <v>15.38847351074219</v>
       </c>
     </row>
     <row r="5">
@@ -616,19 +616,19 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>59.92533493041992</v>
+        <v>78.94721984863281</v>
       </c>
       <c r="H5" t="n">
-        <v>56.98447799682617</v>
+        <v>79.64559936523438</v>
       </c>
       <c r="I5" t="n">
-        <v>2143.89453125</v>
+        <v>2029.939575195312</v>
       </c>
       <c r="J5" t="n">
-        <v>57.37261581420898</v>
+        <v>68.20951843261719</v>
       </c>
       <c r="K5" t="n">
-        <v>9.22816276550293</v>
+        <v>14.93360042572021</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>56.97018051147461</v>
+        <v>80.05066680908203</v>
       </c>
       <c r="H6" t="n">
-        <v>58.22603988647461</v>
+        <v>83.11394500732422</v>
       </c>
       <c r="I6" t="n">
-        <v>1715.078979492188</v>
+        <v>1396.014282226562</v>
       </c>
       <c r="J6" t="n">
-        <v>49.42683792114258</v>
+        <v>60.19478988647461</v>
       </c>
       <c r="K6" t="n">
-        <v>6.28036642074585</v>
+        <v>12.46156311035156</v>
       </c>
     </row>
     <row r="7">
@@ -686,19 +686,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>42.50269317626953</v>
+        <v>69.93710327148438</v>
       </c>
       <c r="H7" t="n">
-        <v>87.46645355224609</v>
+        <v>106.8436660766602</v>
       </c>
       <c r="I7" t="n">
-        <v>1342.947875976562</v>
+        <v>955.1465454101562</v>
       </c>
       <c r="J7" t="n">
-        <v>50.9345588684082</v>
+        <v>63.17579650878906</v>
       </c>
       <c r="K7" t="n">
-        <v>14.04294776916504</v>
+        <v>20.43521499633789</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>55.01007843017578</v>
+        <v>78.05543518066406</v>
       </c>
       <c r="H8" t="n">
-        <v>68.51380157470703</v>
+        <v>98.42250823974609</v>
       </c>
       <c r="I8" t="n">
-        <v>1633.667358398438</v>
+        <v>1116.609252929688</v>
       </c>
       <c r="J8" t="n">
-        <v>49.10960388183594</v>
+        <v>60.35526275634766</v>
       </c>
       <c r="K8" t="n">
-        <v>18.39679718017578</v>
+        <v>25.22410774230957</v>
       </c>
     </row>
     <row r="9">
@@ -756,19 +756,19 @@
         <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>54.21974945068359</v>
+        <v>77.52548217773438</v>
       </c>
       <c r="H9" t="n">
-        <v>81.57511138916016</v>
+        <v>107.4435424804688</v>
       </c>
       <c r="I9" t="n">
-        <v>1374.293090820312</v>
+        <v>893.3269653320312</v>
       </c>
       <c r="J9" t="n">
-        <v>26.4704647064209</v>
+        <v>38.96947860717773</v>
       </c>
       <c r="K9" t="n">
-        <v>11.9194860458374</v>
+        <v>17.95323944091797</v>
       </c>
     </row>
     <row r="10">
@@ -791,19 +791,19 @@
         <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>36.63339233398438</v>
+        <v>66.66901397705078</v>
       </c>
       <c r="H10" t="n">
-        <v>57.39704895019531</v>
+        <v>89.58676910400391</v>
       </c>
       <c r="I10" t="n">
-        <v>1145.97314453125</v>
+        <v>970.6783447265625</v>
       </c>
       <c r="J10" t="n">
-        <v>48.41079330444336</v>
+        <v>49.47676086425781</v>
       </c>
       <c r="K10" t="n">
-        <v>13.73410797119141</v>
+        <v>21.01206970214844</v>
       </c>
     </row>
     <row r="11">
@@ -826,19 +826,19 @@
         <v>19.8</v>
       </c>
       <c r="G11" t="n">
-        <v>50.51754379272461</v>
+        <v>76.20642852783203</v>
       </c>
       <c r="H11" t="n">
-        <v>82.83078765869141</v>
+        <v>108.5938339233398</v>
       </c>
       <c r="I11" t="n">
-        <v>1511.091552734375</v>
+        <v>986.235595703125</v>
       </c>
       <c r="J11" t="n">
-        <v>49.19083023071289</v>
+        <v>46.76139068603516</v>
       </c>
       <c r="K11" t="n">
-        <v>24.22340774536133</v>
+        <v>26.58307266235352</v>
       </c>
     </row>
     <row r="12">
@@ -861,19 +861,19 @@
         <v>24.2</v>
       </c>
       <c r="G12" t="n">
-        <v>54.67883682250977</v>
+        <v>85.97578430175781</v>
       </c>
       <c r="H12" t="n">
-        <v>51.59475326538086</v>
+        <v>72.54359436035156</v>
       </c>
       <c r="I12" t="n">
-        <v>1630.75732421875</v>
+        <v>1297.40869140625</v>
       </c>
       <c r="J12" t="n">
-        <v>71.45391082763672</v>
+        <v>62.37346267700195</v>
       </c>
       <c r="K12" t="n">
-        <v>29.63018226623535</v>
+        <v>29.95810127258301</v>
       </c>
     </row>
     <row r="13">
@@ -896,19 +896,19 @@
         <v>30.8</v>
       </c>
       <c r="G13" t="n">
-        <v>37.83502578735352</v>
+        <v>54.34929275512695</v>
       </c>
       <c r="H13" t="n">
-        <v>47.95979309082031</v>
+        <v>54.828369140625</v>
       </c>
       <c r="I13" t="n">
-        <v>1404.318359375</v>
+        <v>1425.498168945312</v>
       </c>
       <c r="J13" t="n">
-        <v>46.89516830444336</v>
+        <v>43.03635406494141</v>
       </c>
       <c r="K13" t="n">
-        <v>23.43389129638672</v>
+        <v>21.07692909240723</v>
       </c>
     </row>
   </sheetData>
